--- a/input/images/tables/profile_metadata.xlsx
+++ b/input/images/tables/profile_metadata.xlsx
@@ -613,7 +613,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
@@ -708,53 +712,53 @@
       <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B3" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>us-core-appointment</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-appointment</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>US Core Appointment Profile</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-appointment.html</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>us-core-careplan</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-careplan</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>US Core CarePlan Profile</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>StructureDefinition-us-core-careplan.html</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Type changed from CarePlan in DSTU2 to CareTeam in R4</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Argonaut CarePlan Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -774,17 +778,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CONF-0133</t>
+          <t>CONF-0921</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>care plan</t>
+          <t>appointment</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>CarePlan</t>
+          <t>Appointment</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -809,33 +813,33 @@
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>us-core-careteam</t>
+          <t>us-core-careplan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-careplan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>US Core CareTeam Profile</t>
+          <t>US Core CarePlan Profile</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-careteam.html</t>
+          <t>StructureDefinition-us-core-careplan.html</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -846,10 +850,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Type changed from CarePlan in DSTU2 to CareTeam in R4</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Argonaut CareTeam Profile</t>
+          <t>Argonaut CarePlan Profile</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,17 +877,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CONF-0134</t>
+          <t>CONF-0133</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>careteam</t>
+          <t>care plan</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>CareTeam</t>
+          <t>CarePlan</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -902,58 +910,58 @@
       <c r="AM4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>us-core-condition-encounter-diagnosis</t>
+          <t>us-core-careteam</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-encounter-diagnosis</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>US Core Condition Encounter Diagnosis Profile</t>
+          <t>US Core CareTeam Profile</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-condition-encounter-diagnosis.html</t>
+          <t>StructureDefinition-us-core-careteam.html</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>In version 5.0.0 US Core Condition Profile was split into US Core Condition Encounter Diagnosis Profile and US Core Condition Problems and Health Concerns Profile</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut CareTeam Profile</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -968,34 +976,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CONF-0135</t>
+          <t>CONF-0134</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>encounter diagnosis</t>
+          <t>careteam</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/condition-category|encounter-diagnosis</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>CONF-0159</t>
-        </is>
-      </c>
+          <t>CareTeam</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1015,26 +1011,26 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>us-core-condition-problems-health-concerns</t>
+          <t>us-core-condition-encounter-diagnosis</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-problems-health-concerns</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-encounter-diagnosis</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Condition Encounter Diagnosis Profile</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-condition-problems-health-concerns.html</t>
+          <t>StructureDefinition-us-core-condition-encounter-diagnosis.html</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1069,7 +1065,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYBE </t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>problems and health concern</t>
+          <t>encounter diagnosis</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1094,7 +1090,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item</t>
+          <t>http://terminology.hl7.org/CodeSystem/condition-category|encounter-diagnosis</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1104,24 +1100,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>CONF-0160</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/condition-category|health-concern</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>CONF-0158</t>
-        </is>
-      </c>
+          <t>CONF-0159</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1138,26 +1122,26 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>us-core-coverage</t>
+          <t>us-core-condition-problems-health-concerns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-coverage</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-problems-health-concerns</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>US Core Coverage Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-coverage.html</t>
+          <t>StructureDefinition-us-core-condition-problems-health-concerns.html</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1168,14 +1152,18 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>In version 5.0.0 US Core Condition Profile was split into US Core Condition Encounter Diagnosis Profile and US Core Condition Problems and Health Concerns Profile</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -1183,12 +1171,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t xml:space="preserve">MAYBE </t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1198,25 +1186,49 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CONF-0136</t>
+          <t>CONF-0135</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>problems and health concern</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/condition-category|problem-list-item</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>CONF-0160</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/condition-category|health-concern</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>CONF-0158</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
@@ -1233,26 +1245,26 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>us-core-device</t>
+          <t>us-core-coverage</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-device</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-coverage</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-device.html</t>
+          <t>StructureDefinition-us-core-coverage.html</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1263,21 +1275,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>in version 9.0.0 removed the term "implantable" from the official ( canonical ) URL,  name,  and title.</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Argonaut Device Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1287,7 +1295,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1297,17 +1305,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CONF-0137</t>
+          <t>CONF-0136</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>medical device</t>
+          <t>coverage</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1332,33 +1340,33 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>us-core-diagnosticreport-note</t>
+          <t>us-core-device</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-note</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-device</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>US Core DiagnosticReport Profile for Report and Note Exchange</t>
+          <t>US Core Device Profile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-diagnosticreport-note.html</t>
+          <t>StructureDefinition-us-core-device.html</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1369,10 +1377,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>in version 9.0.0 removed the term "implantable" from the official ( canonical ) URL,  name,  and title.</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Device Profile</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1382,7 +1394,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1392,38 +1404,26 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CONF-0138</t>
+          <t>CONF-0137</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>clinical note</t>
+          <t>medical device</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>DiagnosticReport</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>http://loinc.org|LP29684-5</t>
-        </is>
-      </c>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">http://loinc.org|LP29708-2	</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">http://loinc.org|LP7839-6		</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
@@ -1437,39 +1437,43 @@
       <c r="AM9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>us-core-diagnosticreport-lab</t>
+          <t>us-core-devicerequest</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-lab</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-devicerequest</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
+          <t>US Core DeviceRequest Profile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-diagnosticreport-lab.html</t>
+          <t>StructureDefinition-us-core-devicerequest.html</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1479,7 +1483,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Argonaut DiagnosticReport Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1499,24 +1503,20 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CONF-0138</t>
+          <t>CONF-0923</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>laboratory</t>
+          <t>medical device order</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>DiagnosticReport</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/v2-0074|LAB</t>
-        </is>
-      </c>
+          <t>DeviceRequest</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -1538,26 +1538,26 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>us-core-documentreference</t>
+          <t>us-core-diagnosticreport-note</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-note</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile</t>
+          <t>US Core DiagnosticReport Profile for Report and Note Exchange</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-documentreference.html</t>
+          <t>StructureDefinition-us-core-diagnosticreport-note.html</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1578,19 +1578,19 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Argonaut DocumentReference Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>MAYBE</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>SHALL</t>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CONF-0139</t>
+          <t>CONF-0138</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1608,28 +1608,28 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>DocumentReference</t>
+          <t>DiagnosticReport</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-documentreference-category|clinical-note</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>CONF-0166</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>http://loinc.org|LP29684-5</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://loinc.org|LP29708-2	</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http://loinc.org|LP7839-6		</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -1645,26 +1645,26 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>us-core-encounter</t>
+          <t>us-core-diagnosticreport-lab</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-diagnosticreport-lab</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
+          <t>US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-encounter.html</t>
+          <t>StructureDefinition-us-core-diagnosticreport-lab.html</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1685,7 +1685,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut DiagnosticReport Profile</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1705,20 +1705,24 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CONF-0140</t>
+          <t>CONF-0138</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>encounter</t>
+          <t>laboratory</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Encounter</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
+          <t>DiagnosticReport</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/v2-0074|LAB</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
@@ -1740,26 +1744,26 @@
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>us-core-goal</t>
+          <t>us-core-documentreference</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-goal</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-documentreference</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>US Core Goal Profile</t>
+          <t>US Core DocumentReference Profile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-goal.html</t>
+          <t>StructureDefinition-us-core-documentreference.html</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1780,19 +1784,19 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Argonaut Goal Profile</t>
+          <t>Argonaut DocumentReference Profile</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>MAYBE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>SHALL</t>
@@ -1800,22 +1804,34 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CONF-0141</t>
+          <t>CONF-0139</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>goal</t>
+          <t>clinical note</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+          <t>DocumentReference</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-documentreference-category|clinical-note</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>CONF-0166</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1833,28 +1849,32 @@
       <c r="AM13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>us-core-immunization</t>
+          <t>us-core-encounter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>US Core Immunization Profile</t>
+          <t>US Core Encounter Profile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-immunization.html</t>
+          <t>StructureDefinition-us-core-encounter.html</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1875,17 +1895,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Argonaut Immunization Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1895,17 +1915,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CONF-0142</t>
+          <t>CONF-0140</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>immunization</t>
+          <t>encounter</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Immunization</t>
+          <t>Encounter</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -1930,26 +1950,26 @@
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>us-core-location</t>
+          <t>us-core-goal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-location</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-goal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>US Core Location Profile</t>
+          <t>US Core Goal Profile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-location.html</t>
+          <t>StructureDefinition-us-core-goal.html</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1970,7 +1990,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Goal Profile</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1985,18 +2005,22 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>SHALL</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CONF-0156</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>CONF-0141</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>goal</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2019,28 +2043,32 @@
       <c r="AM15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>us-core-medication</t>
+          <t>us-core-immunization</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>US Core Medication Profile</t>
+          <t>US Core Immunization Profile</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medication.html</t>
+          <t>StructureDefinition-us-core-immunization.html</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2061,7 +2089,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Argonaut Medication Profile</t>
+          <t>Argonaut Immunization Profile</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2076,18 +2104,22 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>SHALL</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CONF-0157</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>CONF-0142</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>immunization</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Medication</t>
+          <t>Immunization</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2112,26 +2144,26 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>us-core-medicationrequest</t>
+          <t>us-core-location</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medicationrequest</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-location</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
+          <t>US Core Location Profile</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationrequest.html</t>
+          <t>StructureDefinition-us-core-location.html</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2152,37 +2184,33 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Argonaut MedicationOrder Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>MAY</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CONF-0143</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>prescription</t>
-        </is>
-      </c>
+          <t>CONF-0156</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>MedicationRequest</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2207,37 +2235,37 @@
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>us-core-medicationdispense</t>
+          <t>us-core-medication</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medicationdispense</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>US Core MedicationDispense Profile</t>
+          <t>US Core Medication Profile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense.html</t>
+          <t>StructureDefinition-us-core-medication.html</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2247,37 +2275,33 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Medication Profile</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>SHALL</t>
+          <t>MAY</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CONF-0144</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>dispensed medication</t>
-        </is>
-      </c>
+          <t>CONF-0157</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>MedicationDispense</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2302,26 +2326,26 @@
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>us-core-observation-lab</t>
+          <t>us-core-medicationrequest</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medicationrequest</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-observation-lab.html</t>
+          <t>StructureDefinition-us-core-medicationrequest.html</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2339,14 +2363,10 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>In Version 6.0.0 derived from US Core Observation Clinical Test Result Profile</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Argonaut Observation Results Profile</t>
+          <t>Argonaut MedicationOrder Profile</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2366,34 +2386,22 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CONF-0145</t>
+          <t>CONF-0143</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>laboratory</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|laboratory</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>CONF-0163</t>
-        </is>
-      </c>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -2413,26 +2421,26 @@
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>us-core-observation-pregnancystatus</t>
+          <t>us-core-medicationdispense</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-pregnancystatus</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medicationdispense</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Status Profile</t>
+          <t>US Core MedicationDispense Profile</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-observation-pregnancystatus.html</t>
+          <t>StructureDefinition-us-core-medicationdispense.html</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2458,12 +2466,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2473,34 +2481,22 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CONF-0145</t>
+          <t>CONF-0144</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>social history</t>
+          <t>dispensed medication</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>CONF-0162</t>
-        </is>
-      </c>
+          <t>MedicationDispense</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -2518,39 +2514,43 @@
       <c r="AM20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>us-core-observation-pregnancyintent</t>
+          <t>us-core-medicationadministration</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-pregnancyintent</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medicationadministration</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Intent Profile</t>
+          <t>US Core MedicationAdministration Profile</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-observation-pregnancyintent.html</t>
+          <t>StructureDefinition-us-core-medicationadministration.html</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2580,34 +2580,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CONF-0145</t>
+          <t>CONF-0922</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>social history</t>
+          <t>administered medication</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>CONF-0162</t>
-        </is>
-      </c>
+          <t>MedicationAdministration</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -2625,39 +2613,43 @@
       <c r="AM21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>us-core-observation-occupation</t>
+          <t>us-core-nutritionorder</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-occupation</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-nutritionorder</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>US Core Observation Occupation Profile</t>
+          <t>US Core NutritionOrder Profile</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-observation-occupation.html</t>
+          <t>StructureDefinition-us-core-nutritionorder.html</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -2672,7 +2664,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2687,34 +2679,22 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CONF-0145</t>
+          <t>CONF-0924</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>social history</t>
+          <t>nutrition order</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>CONF-0162</t>
-        </is>
-      </c>
+          <t>NutritionOrder</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -2734,26 +2714,26 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>us-core-respiratory-rate</t>
+          <t>us-core-observation-lab</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-respiratory-rate</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>US Core Respiratory Rate Profile</t>
+          <t>US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-respiratory-rate.html</t>
+          <t>StructureDefinition-us-core-observation-lab.html</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2764,7 +2744,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2773,12 +2753,12 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+          <t>In Version 6.0.0 derived from US Core Observation Clinical Test Result Profile</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Observation Results Profile</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2788,7 +2768,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2803,7 +2783,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>vital signs</t>
+          <t>laboratory</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2813,7 +2793,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|laboratory</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2823,7 +2803,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>CONF-0165</t>
+          <t>CONF-0163</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -2845,26 +2825,26 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>us-core-simple-observation</t>
+          <t>us-core-observation-pregnancystatus</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-simple-observation</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-pregnancystatus</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile</t>
+          <t>US Core Observation Pregnancy Status Profile</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-simple-observation.html</t>
+          <t>StructureDefinition-us-core-observation-pregnancystatus.html</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2882,11 +2862,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Replaces US Core Observation Social History Profile</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -2894,14 +2870,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>MAYBE</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>MAYBE</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>SHALL</t>
@@ -2914,7 +2890,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>assessment</t>
+          <t>social history</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2924,7 +2900,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
+          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2934,35 +2910,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>CONF-0161</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
-        </is>
-      </c>
+          <t>CONF-0162</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|disability-status</t>
-        </is>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|cognitive-status</t>
-        </is>
-      </c>
+      <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|activity</t>
-        </is>
-      </c>
+      <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
@@ -2972,48 +2932,44 @@
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>us-core-heart-rate</t>
+          <t>us-core-observation-pregnancyintent</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-heart-rate</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-pregnancyintent</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>US Core Heart Rate Profile</t>
+          <t>US Core Observation Pregnancy Intent Profile</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-heart-rate.html</t>
+          <t>StructureDefinition-us-core-observation-pregnancyintent.html</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -3041,7 +2997,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>vital signs</t>
+          <t>social history</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3051,7 +3007,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3061,7 +3017,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>CONF-0165</t>
+          <t>CONF-0162</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3083,48 +3039,44 @@
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>us-core-body-temperature</t>
+          <t>us-core-observation-occupation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-body-temperature</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-occupation</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>US Core Body Temperature Profile</t>
+          <t>US Core Observation Occupation Profile</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-body-temperature.html</t>
+          <t>StructureDefinition-us-core-observation-occupation.html</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -3132,7 +3084,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3152,7 +3104,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>vital signs</t>
+          <t>social history</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3162,7 +3114,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3172,7 +3124,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>CONF-0165</t>
+          <t>CONF-0162</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3194,26 +3146,26 @@
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>pediatric-weight-for-height</t>
+          <t>us-core-respiratory-rate</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/pediatric-weight-for-height</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-respiratory-rate</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>US Core Pediatric Weight for Height Observation Profile</t>
+          <t>US Core Respiratory Rate Profile</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>StructureDefinition-pediatric-weight-for-height.html</t>
+          <t>StructureDefinition-us-core-respiratory-rate.html</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3224,7 +3176,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3233,7 +3185,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
+          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3305,37 +3257,37 @@
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>us-core-pulse-oximetry</t>
+          <t>us-core-simple-observation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-pulse-oximetry</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-simple-observation</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>US Core Pulse Oximetry Profile</t>
+          <t>US Core Simple Observation Profile</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-pulse-oximetry.html</t>
+          <t>StructureDefinition-us-core-simple-observation.html</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3344,7 +3296,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
+          <t>Replaces US Core Observation Social History Profile</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3354,12 +3306,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3374,7 +3326,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>vital signs</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3384,7 +3336,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3394,19 +3346,35 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>CONF-0165</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
+          <t>CONF-0161</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
+        </is>
+      </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|disability-status</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|cognitive-status</t>
+        </is>
+      </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|activity</t>
+        </is>
+      </c>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
@@ -3416,57 +3384,61 @@
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>us-core-smokingstatus</t>
+          <t>us-core-heart-rate</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-smokingstatus</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-heart-rate</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>US Core Smoking Status Observation Profile</t>
+          <t>US Core Heart Rate Profile</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-smokingstatus.html</t>
+          <t>StructureDefinition-us-core-heart-rate.html</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Argonaut Smoking Status Observation Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3481,7 +3453,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>social history</t>
+          <t>vital signs</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3491,7 +3463,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -3501,7 +3473,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>CONF-0162</t>
+          <t>CONF-0165</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -3523,37 +3495,37 @@
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>us-core-observation-sexual-orientation</t>
+          <t>us-core-body-temperature</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-sexual-orientation</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-body-temperature</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>US Core Observation Sexual Orientation Profile</t>
+          <t>US Core Body Temperature Profile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>!StructureDefinition-us-core-observation-sexual-orientation.html</t>
+          <t>StructureDefinition-us-core-body-temperature.html</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3562,7 +3534,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>After version 7.0.0 this extension is no longer a USCDI requirement.</t>
+          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3592,7 +3564,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>social history</t>
+          <t>vital signs</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3602,7 +3574,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -3612,7 +3584,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>CONF-0162</t>
+          <t>CONF-0165</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -3634,26 +3606,26 @@
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>us-core-head-circumference</t>
+          <t>pediatric-weight-for-height</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-head-circumference</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/pediatric-weight-for-height</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>US Core Head Circumference Profile</t>
+          <t>US Core Pediatric Weight for Height Observation Profile</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-head-circumference.html</t>
+          <t>StructureDefinition-pediatric-weight-for-height.html</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3664,7 +3636,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3673,7 +3645,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3745,26 +3717,26 @@
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>us-core-body-height</t>
+          <t>us-core-pulse-oximetry</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-body-height</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-pulse-oximetry</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>US Core Body Height Profile</t>
+          <t>US Core Pulse Oximetry Profile</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-body-height.html</t>
+          <t>StructureDefinition-us-core-pulse-oximetry.html</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3775,7 +3747,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -3784,7 +3756,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3854,39 +3826,43 @@
       <c r="AM32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B33" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>us-core-bmi</t>
+          <t>us-core-smokingstatus</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-bmi</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-smokingstatus</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>US Core BMI Profile</t>
+          <t>US Core Tobacco And Nicotine Use Observation Profile</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-bmi.html</t>
+          <t>StructureDefinition-us-core-smokingstatus.html</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -3895,22 +3871,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+          <t>In version 10.0.0 the title changed from "US Core Smoking Status Observation Profile" to "US Core Tobacco And Nicotine Use Observation Profile" and the name from USCoreSmokingStatusProfile to USCoreTobaccoAndNicotineUseObservationProfile. The id and canonical URL are unchanged and still use "smokingstatus"</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Smoking Status Observation Profile</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3925,7 +3901,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>vital signs</t>
+          <t>social history</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3935,7 +3911,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3945,7 +3921,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>CONF-0165</t>
+          <t>CONF-0162</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -3967,26 +3943,26 @@
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>us-core-observation-screening-assessment</t>
+          <t>us-core-observation-sexual-orientation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-screening-assessment</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-sexual-orientation</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>US Core Observation Screening Assessment Profile</t>
+          <t>US Core Observation Sexual Orientation Profile</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-observation-screening-assessment.html</t>
+          <t>!StructureDefinition-us-core-observation-sexual-orientation.html</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3997,7 +3973,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4006,7 +3982,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Replaces US Core Observation Survey Profile and US Core Observation SDOH Assessment Profile</t>
+          <t>After version 7.0.0 this extension is no longer a USCDI requirement.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4036,7 +4012,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>assessment</t>
+          <t>social history</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4046,7 +4022,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|survey</t>
+          <t>http://terminology.hl7.org//CodeSystem-observation-category|social-history</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4056,94 +4032,70 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>CONF-0164</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>CONF-0161</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
-        </is>
-      </c>
+          <t>CONF-0162</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|disability-status</t>
-        </is>
-      </c>
+      <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|cognitive-status</t>
-        </is>
-      </c>
+      <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|activity</t>
-        </is>
-      </c>
+      <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>us-core-average-blood-pressure</t>
+          <t>us-core-head-circumference</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-average-blood-pressure</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-head-circumference</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>US Core Average Blood Pressure Profile</t>
+          <t>US Core Head Circumference Profile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-average-blood-pressure.html</t>
+          <t>StructureDefinition-us-core-head-circumference.html</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7.0.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -4151,7 +4103,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -4213,26 +4165,26 @@
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>us-core-blood-pressure</t>
+          <t>us-core-body-height</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-blood-pressure</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-body-height</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>US Core Blood Pressure Profile</t>
+          <t>US Core Body Height Profile</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-blood-pressure.html</t>
+          <t>StructureDefinition-us-core-body-height.html</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4324,37 +4276,37 @@
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>us-core-observation-clinical-result</t>
+          <t>us-core-bmi</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-clinical-result</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-bmi</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>US Core Observation Clinical Result Profile</t>
+          <t>US Core BMI Profile</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-observation-clinical-result.html</t>
+          <t>StructureDefinition-us-core-bmi.html</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4363,7 +4315,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Replaces US Core Observation Clinical Test Result Profile and US Core Observation Imaging Result Profile</t>
+          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4378,7 +4330,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4393,7 +4345,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>clinical results</t>
+          <t>vital signs</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,23 +4355,23 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|laboratory</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|imaging</t>
-        </is>
-      </c>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|procedure</t>
-        </is>
-      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
@@ -4435,37 +4387,37 @@
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pediatric-bmi-for-age</t>
+          <t>us-core-observation-screening-assessment</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/pediatric-bmi-for-age</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-screening-assessment</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>US Core Pediatric BMI for Age Observation Profile</t>
+          <t>US Core Observation Screening Assessment Profile</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>StructureDefinition-pediatric-bmi-for-age.html</t>
+          <t>StructureDefinition-us-core-observation-screening-assessment.html</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4474,7 +4426,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
+          <t>Replaces US Core Observation Survey Profile and US Core Observation SDOH Assessment Profile</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4504,7 +4456,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>vital signs</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4514,7 +4466,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|survey</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -4524,70 +4476,94 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>CONF-0165</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
+          <t>CONF-0164</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>CONF-0161</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|disability-status</t>
+        </is>
+      </c>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|cognitive-status</t>
+        </is>
+      </c>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|activity</t>
+        </is>
+      </c>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>head-occipital-frontal-circumference-percentile</t>
+          <t>us-core-average-blood-pressure</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/head-occipital-frontal-circumference-percentile</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-average-blood-pressure</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>US Core Pediatric Head Occipital Frontal Circumference Percentile Profile</t>
+          <t>US Core Average Blood Pressure Profile</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>StructureDefinition-head-occipital-frontal-circumference-percentile.html</t>
+          <t>StructureDefinition-us-core-average-blood-pressure.html</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>7.0.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -4595,7 +4571,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4657,26 +4633,26 @@
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>us-core-body-weight</t>
+          <t>us-core-blood-pressure</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-body-weight</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-blood-pressure</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>US Core Body Weight Profile</t>
+          <t>US Core Blood Pressure Profile</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-body-weight.html</t>
+          <t>StructureDefinition-us-core-blood-pressure.html</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -4768,37 +4744,37 @@
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>us-core-vital-signs</t>
+          <t>us-core-observation-clinical-result</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-vital-signs</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-clinical-result</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>US Core Vital Signs Profile</t>
+          <t>US Core Observation Clinical Result Profile</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-vital-signs.html</t>
+          <t>StructureDefinition-us-core-observation-clinical-result.html</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -4807,12 +4783,12 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+          <t>Replaces US Core Observation Clinical Test Result Profile and US Core Observation Imaging Result Profile</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Argonaut Vital Signs Observation Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4822,7 +4798,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4837,7 +4813,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>vital signs</t>
+          <t>clinical results</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4847,23 +4823,23 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>SHALL</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>CONF-0165</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|laboratory</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|imaging</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|procedure</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
@@ -4879,26 +4855,26 @@
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>us-core-organization</t>
+          <t>pediatric-bmi-for-age</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/pediatric-bmi-for-age</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>US Core Organization Profile</t>
+          <t>US Core Pediatric BMI for Age Observation Profile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-organization.html</t>
+          <t>StructureDefinition-pediatric-bmi-for-age.html</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -4916,7 +4892,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -4924,14 +4904,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>SHALL</t>
@@ -4939,22 +4919,34 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>CONF-0146</t>
+          <t>CONF-0145</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>vital signs</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Organization</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
@@ -4974,26 +4966,26 @@
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>us-core-patient</t>
+          <t>head-occipital-frontal-circumference-percentile</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/head-occipital-frontal-circumference-percentile</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Pediatric Head Occipital Frontal Circumference Percentile Profile</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-patient.html</t>
+          <t>StructureDefinition-head-occipital-frontal-circumference-percentile.html</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5011,20 +5003,24 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3.1.1* based on the FHIR Vital Signs Profile, 4.0.0+ based on the US Core Vital Signs Profile</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Argonaut Patient Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5034,22 +5030,34 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>CONF-0147</t>
+          <t>CONF-0145</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>vital signs</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
@@ -5069,26 +5077,26 @@
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>us-core-practitioner</t>
+          <t>us-core-body-weight</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-body-weight</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
+          <t>US Core Body Weight Profile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-practitioner.html</t>
+          <t>StructureDefinition-us-core-body-weight.html</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5099,14 +5107,18 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -5119,7 +5131,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5129,22 +5141,34 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>CONF-0148</t>
+          <t>CONF-0145</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>practitioner</t>
+          <t>vital signs</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Practitioner</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
@@ -5164,26 +5188,26 @@
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>us-core-practitionerrole</t>
+          <t>us-core-vital-signs</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-vital-signs</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>US Core PractitionerRole Profile</t>
+          <t>US Core Vital Signs Profile</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-practitionerrole.html</t>
+          <t>StructureDefinition-us-core-vital-signs.html</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5194,17 +5218,21 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>4.0.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Previous to version 4.0.0, referenced the FHIR Vital Signs Profile</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Vital Signs Observation Profile</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5214,7 +5242,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5224,22 +5252,34 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>CONF-0149</t>
+          <t>CONF-0145</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>practitioner role</t>
+          <t>vital signs</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>PractitionerRole</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>http://terminology.hl7.org/CodeSystem/observation-category|vital-signs</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>CONF-0165</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
@@ -5259,26 +5299,26 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>us-core-procedure</t>
+          <t>us-core-organization</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-procedure</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile</t>
+          <t>US Core Organization Profile</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-procedure.html</t>
+          <t>StructureDefinition-us-core-organization.html</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5299,7 +5339,7 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Argonaut Procedure Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5309,7 +5349,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5319,17 +5359,17 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>CONF-0150</t>
+          <t>CONF-0146</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>procedure</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Procedure</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -5354,26 +5394,26 @@
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>us-core-provenance</t>
+          <t>us-core-patient</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-provenance</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>US Core Provenance Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-provenance.html</t>
+          <t>StructureDefinition-us-core-patient.html</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5394,17 +5434,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Patient Profile</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5414,17 +5454,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>CONF-0151</t>
+          <t>CONF-0147</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Patient</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -5449,37 +5489,37 @@
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>us-core-questionnaireresponse</t>
+          <t>us-core-practitioner</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-questionnaireresponse</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>US Core QuestionnaireResponse Profile</t>
+          <t>US Core Practitioner Profile</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-questionnaireresponse.html</t>
+          <t>StructureDefinition-us-core-practitioner.html</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5494,12 +5534,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5509,17 +5549,17 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CONF-0152</t>
+          <t>CONF-0148</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>completed questionnnaire, survey and assessement</t>
+          <t>practitioner</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>QuestionnaireResponse</t>
+          <t>Practitioner</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -5544,37 +5584,37 @@
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>us-core-relatedperson</t>
+          <t>us-core-practitionerrole</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>US Core RelatedPerson Profile</t>
+          <t>US Core PractitionerRole Profile</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-relatedperson.html</t>
+          <t>StructureDefinition-us-core-practitionerrole.html</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -5589,12 +5629,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5604,17 +5644,17 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>CONF-0153</t>
+          <t>CONF-0149</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>related person</t>
+          <t>practitioner role</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>RelatedPerson</t>
+          <t>PractitionerRole</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -5637,39 +5677,43 @@
       <c r="AM49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B50" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>us-core-servicerequest</t>
+          <t>us-core-procedure</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-servicerequest</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-procedure</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Procedure Profile</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-servicerequest.html</t>
+          <t>StructureDefinition-us-core-procedure.html</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -5679,7 +5723,7 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Procedure Profile</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5689,7 +5733,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MAYBE</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5699,42 +5743,26 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>CONF-0154</t>
+          <t>CONF-0150</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>order and referral</t>
+          <t>procedure</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>ServiceRequest</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
-        </is>
-      </c>
+      <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>http://snomed.info/sct|surgical-procedure</t>
-        </is>
-      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
@@ -5750,37 +5778,37 @@
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>us-core-specimen</t>
+          <t>us-core-provenance</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-specimen</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-provenance</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core Provenance Profile</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-specimen.html</t>
+          <t>StructureDefinition-us-core-provenance.html</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -5800,7 +5828,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5810,17 +5838,17 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>CONF-0155</t>
+          <t>CONF-0151</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>specimen</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Specimen</t>
+          <t>Provenance</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -5845,37 +5873,37 @@
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>us-core-treatment-intervention-preference</t>
+          <t>us-core-questionnaireresponse</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-treatment-intervention-preference</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-questionnaireresponse</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>US Core Treatment Intervention Preference Profile</t>
+          <t>US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-treatment-intervention-preference.html</t>
+          <t>StructureDefinition-us-core-questionnaireresponse.html</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7.0.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -5890,7 +5918,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5905,29 +5933,21 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>CONF-0145</t>
+          <t>CONF-0152</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>treatment intervention preference</t>
+          <t>completed questionnnaire, survey and assessement</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|treatment-intervention-preference</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+          <t>QuestionnaireResponse</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
@@ -5946,39 +5966,43 @@
       <c r="AM52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B53" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>us-core-care-experience-preference</t>
+          <t>us-core-relatedperson</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-care-experience-preference</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>US Core Care Experience Preference Profile</t>
+          <t>US Core RelatedPerson Profile</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-care-experience-preference.html</t>
+          <t>StructureDefinition-us-core-relatedperson.html</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7.0.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -5993,7 +6017,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>MAYBE</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -6008,29 +6032,21 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>CONF-0145</t>
+          <t>CONF-0153</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>care experience preference</t>
+          <t>related person</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|care-experience-preference</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
+          <t>RelatedPerson</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
@@ -6051,37 +6067,37 @@
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>us-core-familymemberhistory</t>
+          <t>us-core-servicerequest</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-familymemberhistory</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-servicerequest</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>US Core FamilyMemberHistory Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-familymemberhistory.html</t>
+          <t>StructureDefinition-us-core-servicerequest.html</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>9.0.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6111,26 +6127,42 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CONF-0909</t>
+          <t>CONF-0154</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>family health history</t>
+          <t>order and referral</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>FamilyMemberHistory</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+          <t>ServiceRequest</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|sdoh</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|functional-status</t>
+        </is>
+      </c>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>http://snomed.info/sct|surgical-procedure</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
@@ -6144,47 +6176,83 @@
       <c r="AM54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B55" t="n">
-        <v>63</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>us-core-specimen</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-specimen</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+          <t>US Core Specimen Profile</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-specimen.html</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6.0.0</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>3.1.1*</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>US Core MedicationStatement Profile not defined in 3.1.1*</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Argonaut MedicationStatement Profile</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+          <t xml:space="preserve">     -</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>MAYBE</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CONF-0155</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>specimen</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>MedicationStatement</t>
+          <t>Specimen</t>
         </is>
       </c>
       <c r="V55" t="inlineStr"/>
@@ -6209,57 +6277,89 @@
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>66</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>us-core-treatment-intervention-preference</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-treatment-intervention-preference</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>US Core Condition Profile</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>US Core Treatment Intervention Preference Profile</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-treatment-intervention-preference.html</t>
+        </is>
+      </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>7.0.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>5.0.0</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>In version 5.0.0 US Core Condition Profile was split into US Core Condition Encounter Diagnosis Profile and US Core Condition Problems and Health Concerns Profile</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Argonaut Condition Profile</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
+          <t xml:space="preserve">     -</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>MAYBE</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>treatment intervention preference</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|treatment-intervention-preference</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
@@ -6280,26 +6380,26 @@
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>us-core-adi-documentreference</t>
+          <t>us-core-care-experience-preference</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-adi-documentreference</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-care-experience-preference</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>US Core ADI DocumentReference Profile</t>
+          <t>US Core Care Experience Preference Profile</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-adi-documentreference.html</t>
+          <t>StructureDefinition-us-core-care-experience-preference.html</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6310,7 +6410,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8.0.0</t>
+          <t>7.0.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -6325,32 +6425,44 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
+          <t>MAYBE</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="R57" t="inlineStr">
         <is>
           <t>SHALL</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>adi</t>
+          <t>care experience preference</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>DocumentReference</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/CodeSystem/us-core-category|care-experience-preference</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
@@ -6371,26 +6483,26 @@
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>us-core-observation-adi-documentation</t>
+          <t>us-core-familymemberhistory</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-adi-documentation</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-familymemberhistory</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>US Core Observation ADI Documentation Profile</t>
+          <t>US Core FamilyMemberHistory Profile</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-observation-adi-documentation.html</t>
+          <t>StructureDefinition-us-core-familymemberhistory.html</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6401,7 +6513,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8.0.0</t>
+          <t>9.0.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -6429,15 +6541,19 @@
           <t>SHALL</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>CONF-0909</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>adi</t>
+          <t>family health history</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>FamilyMemberHistory</t>
         </is>
       </c>
       <c r="V58" t="inlineStr"/>
@@ -6462,45 +6578,35 @@
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>US Core Observation Imaging Result Profile</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5.0.0</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Superseded by US Core Observation Clinical Result Profile in version 6.0.0</t>
+          <t>US Core MedicationStatement Profile not defined in 3.1.1*</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut MedicationStatement Profile</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -6510,7 +6616,7 @@
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>MedicationStatement</t>
         </is>
       </c>
       <c r="V59" t="inlineStr"/>
@@ -6535,45 +6641,43 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>US Core Observation Clinical Test Result Profile</t>
+          <t>US Core Condition Profile</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>3</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="H60" t="n">
+        <v>5</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>3.1.1*</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Superseded by US Core Observation Clinical Result Profile in version 6.0.0</t>
+          <t>In version 5.0.0 US Core Condition Profile was split into US Core Condition Encounter Diagnosis Profile and US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut Condition Profile</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -6583,7 +6687,7 @@
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="V60" t="inlineStr"/>
@@ -6608,55 +6712,77 @@
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>71</v>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>us-core-adi-documentreference</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-adi-documentreference</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>US Core Observation SDOH Assessment Profile</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>US Core ADI DocumentReference Profile</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-adi-documentreference.html</t>
+        </is>
+      </c>
       <c r="G61" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>8.0.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>6.0.0</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Superseded by US Core Observation Screening Assessment Profile in version 6.0.0</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>CONF-0139</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>adi</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="V61" t="inlineStr"/>
@@ -6681,52 +6807,74 @@
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>72</v>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>us-core-observation-adi-documentation</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-adi-documentation</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>US Core Observation Survey Profile</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>US Core Observation ADI Documentation Profile</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-observation-adi-documentation.html</t>
+        </is>
+      </c>
       <c r="G62" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>8.0.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>6.0.0</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Superseded by US Core Observation Screening Assessment Profile in version 6.0.0</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>CONF-0145</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>adi</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>Observation</t>
@@ -6754,13 +6902,13 @@
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>US Core Observation Social History Profile</t>
+          <t>US Core Observation Imaging Result Profile</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -6787,7 +6935,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Superseded by US Core Simple Observation Profile in version 6.0.0</t>
+          <t>Superseded by US Core Observation Clinical Result Profile in version 6.0.0</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6827,44 +6975,42 @@
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>76</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>us-core-tribal-affiliation</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-tribal-affiliation</t>
-        </is>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>US Core Tribal Affiliation Extension</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>StructureDefinition-us-core-tribal-affiliation.html</t>
-        </is>
-      </c>
+          <t>US Core Observation Clinical Test Result Profile</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>3</v>
       </c>
-      <c r="H64" t="n">
-        <v>3</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>5.0.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>6.0.0</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Superseded by US Core Observation Clinical Result Profile in version 6.0.0</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -6877,7 +7023,7 @@
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="V64" t="inlineStr"/>
@@ -6902,50 +7048,40 @@
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>77</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>us-core-genderIdentity</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-genderIdentity</t>
-        </is>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>US Core Gender Identity Extension</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>StructureDefinition-us-core-genderIdentity.html</t>
-        </is>
-      </c>
+          <t>US Core Observation SDOH Assessment Profile</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>3</v>
       </c>
-      <c r="H65" t="n">
-        <v>3</v>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>5.0.0</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>8.0.0</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>6.0.0</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>After version 7.0.0 this extension is no longer a USCDI requirement and has been deprecated.</t>
+          <t>Superseded by US Core Observation Screening Assessment Profile in version 6.0.0</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6960,7 +7096,7 @@
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="V65" t="inlineStr"/>
@@ -6985,48 +7121,42 @@
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>78</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>us-core-jurisdiction</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-jurisdiction</t>
-        </is>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>US Core Jurisdiction Extension</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>StructureDefinition-us-core-jurisdiction.html</t>
-        </is>
-      </c>
+          <t>US Core Observation Survey Profile</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>3</v>
       </c>
-      <c r="H66" t="n">
-        <v>2</v>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>5.0.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>6.0.0</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Superseded by US Core Observation Screening Assessment Profile in version 6.0.0</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -7039,7 +7169,7 @@
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="V66" t="inlineStr"/>
@@ -7064,48 +7194,40 @@
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>79</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>us-core-individual-sex</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-individual-sex</t>
-        </is>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>US Core Individual Sex Extension</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>StructureDefinition-us-core-individual-sex.html</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+          <t>US Core Observation Social History Profile</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="H67" t="n">
-        <v>5</v>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8.0.1</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>6.0.0</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Supersedes the US Core Sex Extension.</t>
+          <t>Superseded by US Core Simple Observation Profile in version 6.0.0</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -7120,7 +7242,7 @@
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="V67" t="inlineStr"/>
@@ -7145,37 +7267,37 @@
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>us-core-medication-adherence</t>
+          <t>us-core-tribal-affiliation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication-adherence</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-tribal-affiliation</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>US Core Medication Adherence Extension</t>
+          <t>US Core Tribal Affiliation Extension</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medication-adherence.html</t>
+          <t>StructureDefinition-us-core-tribal-affiliation.html</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7.0.0</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -7220,44 +7342,52 @@
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>us-core-interpreter-needed</t>
+          <t>us-core-genderIdentity</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-interpreter-needed</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-genderIdentity</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>US Core Interpreter Needed Extension</t>
+          <t>US Core Gender Identity Extension</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-interpreter-needed.html</t>
+          <t>StructureDefinition-us-core-genderIdentity.html</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>5.0.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>8.0.0</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>After version 7.0.0 this extension is no longer a USCDI requirement and has been deprecated.</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -7295,26 +7425,26 @@
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>us-core-sex</t>
+          <t>us-core-jurisdiction</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-sex</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-jurisdiction</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>US Core Sex Extension</t>
+          <t>US Core Jurisdiction Extension</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-sex.html</t>
+          <t>StructureDefinition-us-core-jurisdiction.html</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -7325,22 +7455,18 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6.1.0</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>8.0.1</t>
-        </is>
-      </c>
+          <t>6.0.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Superseded  in version 8.0.1 by the US Core Individual Sex Extension.</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -7378,44 +7504,50 @@
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>us-core-extension-questionnaire-uri</t>
+          <t>us-core-individual-sex</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-extension-questionnaire-uri</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-individual-sex</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>US Core Extension Questionnaire URI</t>
+          <t>US Core Individual Sex Extension</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-extension-questionnaire-uri.html</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>3</v>
+          <t>StructureDefinition-us-core-individual-sex.html</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>8.0.1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Supersedes the US Core Sex Extension.</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -7453,52 +7585,44 @@
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>uscdi-requirement</t>
+          <t>us-core-medication-adherence</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/uscdi-requirement</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-medication-adherence</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>US Core USCDI Requirement Extension</t>
+          <t>US Core Medication Adherence Extension</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>StructureDefinition-uscdi-requirement.html</t>
+          <t>StructureDefinition-us-core-medication-adherence.html</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>6.0.0</t>
+          <t>7.0.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>This extension is only used on US Core Profile StructureDefinition elements</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -7536,47 +7660,43 @@
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>us-core-direct</t>
+          <t>us-core-interpreter-needed</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-direct</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-interpreter-needed</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>US Core Direct email Extension</t>
+          <t>US Core Interpreter Needed Extension</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-direct.html</t>
+          <t>StructureDefinition-us-core-interpreter-needed.html</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>8.0.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
@@ -7615,47 +7735,55 @@
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>us-core-ethnicity</t>
+          <t>us-core-sex</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-ethnicity</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-sex</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>US Core Ethnicity Extension</t>
+          <t>US Core Sex Extension</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-ethnicity.html</t>
+          <t>StructureDefinition-us-core-sex.html</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
+          <t>6.1.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>8.0.1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Superseded  in version 8.0.1 by the US Core Individual Sex Extension.</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Argonaut ethnicity Extension</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -7690,55 +7818,47 @@
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>us-core-birthsex</t>
+          <t>us-core-extension-questionnaire-uri</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-birthsex</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-extension-questionnaire-uri</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>US Core Birth Sex Extension</t>
+          <t>US Core Extension Questionnaire URI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-birthsex.html</t>
+          <t>StructureDefinition-us-core-extension-questionnaire-uri.html</t>
         </is>
       </c>
       <c r="G75" t="n">
         <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3.1.1*</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>After version 6.0.0 this extension is no longer a USCDI requirement.</t>
-        </is>
-      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Sex of patient assigned at birth</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -7773,46 +7893,52 @@
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>us-core-familymemberhistory-recorder</t>
+          <t>uscdi-requirement</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-familymemberhistory-recorder</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/uscdi-requirement</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>US Core FamilyMemberHistory Recorder Extension</t>
+          <t>US Core USCDI Requirement Extension</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-familymemberhistory-recorder.html</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+          <t>StructureDefinition-uscdi-requirement.html</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>3</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>9.0.0</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>This extension is only used on US Core Profile StructureDefinition elements</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t xml:space="preserve">     -</t>
@@ -7850,33 +7976,33 @@
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>us-core-race</t>
+          <t>us-core-direct</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-race</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-direct</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>US Core Race Extension</t>
+          <t>US Core Direct email Extension</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-race.html</t>
+          <t>StructureDefinition-us-core-direct.html</t>
         </is>
       </c>
       <c r="G77" t="n">
         <v>3</v>
       </c>
       <c r="H77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -7886,11 +8012,15 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Argonaut Race Extension</t>
+          <t xml:space="preserve">     -</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -7925,55 +8055,47 @@
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>us-core-authentication-time</t>
+          <t>us-core-ethnicity</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-authentication-time</t>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-ethnicity</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>US Core Authentication Time Extension</t>
+          <t>US Core Ethnicity Extension</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-authentication-time.html</t>
+          <t>StructureDefinition-us-core-ethnicity.html</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>8.0.0</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>9.0.0</t>
-        </is>
-      </c>
+          <t>3.1.1*</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Has been superseded by the standard Cross-version Extension for R5.DocumentReference.attester for use in FHIR R4 and is deprecated.</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">     -</t>
+          <t>Argonaut ethnicity Extension</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -7981,7 +8103,11 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
@@ -8001,6 +8127,320 @@
       <c r="AL78" t="inlineStr"/>
       <c r="AM78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>87</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>us-core-birthsex</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-birthsex</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>US Core Birth Sex Extension</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-birthsex.html</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>5</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3.1.1*</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>After version 6.0.0 this extension is no longer a USCDI requirement.</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Sex of patient assigned at birth</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>88</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>us-core-familymemberhistory-recorder</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-familymemberhistory-recorder</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>US Core FamilyMemberHistory Recorder Extension</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-familymemberhistory-recorder.html</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>9.0.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     -</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>89</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>us-core-race</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-race</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>US Core Race Extension</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-race.html</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>3</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3.1.1*</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Argonaut Race Extension</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="n">
+        <v>90</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>us-core-authentication-time</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-authentication-time</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>US Core Authentication Time Extension</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-authentication-time.html</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8.0.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>9.0.0</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Has been superseded by the standard Cross-version Extension for R5.DocumentReference.attester for use in FHIR R4 and is deprecated.</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     -</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
